--- a/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -13322,11 +13322,11 @@
       </c>
       <c r="F170" s="15" t="inlineStr">
         <is>
-          <t>혼자여도 상 차려 먹기</t>
+          <t>대충 때우지 않고 차려 먹기</t>
         </is>
       </c>
       <c r="G170" s="15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
@@ -13354,7 +13354,11 @@
         </is>
       </c>
       <c r="M170" s="1" t="n"/>
-      <c r="N170" s="3" t="n"/>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O170" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0204</t>
@@ -13466,11 +13470,11 @@
       </c>
       <c r="F172" s="1" t="inlineStr">
         <is>
-          <t>혼밥에도 채소 한 가지</t>
+          <t>간단히 먹어도 채소 하나</t>
         </is>
       </c>
       <c r="G172" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
@@ -13498,7 +13502,11 @@
         </is>
       </c>
       <c r="M172" s="1" t="n"/>
-      <c r="N172" s="3" t="n"/>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O172" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0206</t>
@@ -13610,7 +13618,7 @@
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t>도시락에 채소 한 칸</t>
+          <t>채소 반찬 미리 담기</t>
         </is>
       </c>
       <c r="G174" s="1" t="n">
@@ -13642,7 +13650,11 @@
         </is>
       </c>
       <c r="M174" s="1" t="n"/>
-      <c r="N174" s="3" t="n"/>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O174" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0208</t>
@@ -13682,11 +13694,11 @@
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t>도시락에 달걀 하나</t>
+          <t>달걀 반찬 하나 챙기기</t>
         </is>
       </c>
       <c r="G175" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
@@ -13714,7 +13726,11 @@
         </is>
       </c>
       <c r="M175" s="1" t="n"/>
-      <c r="N175" s="3" t="n"/>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O175" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0209</t>
@@ -13754,11 +13770,11 @@
       </c>
       <c r="F176" s="1" t="inlineStr">
         <is>
-          <t>도시락 국물은 빼기</t>
+          <t>국물 반찬은 빼고 담기</t>
         </is>
       </c>
       <c r="G176" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
@@ -13786,7 +13802,11 @@
         </is>
       </c>
       <c r="M176" s="1" t="n"/>
-      <c r="N176" s="3" t="n"/>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O176" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0210</t>
@@ -13826,11 +13846,11 @@
       </c>
       <c r="F177" s="1" t="inlineStr">
         <is>
-          <t>도시락 반찬은 구이로</t>
+          <t>반찬은 튀김 대신 구이로</t>
         </is>
       </c>
       <c r="G177" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -13858,7 +13878,11 @@
         </is>
       </c>
       <c r="M177" s="1" t="n"/>
-      <c r="N177" s="3" t="n"/>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O177" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0211</t>
@@ -13898,15 +13922,15 @@
       </c>
       <c r="F178" s="15" t="inlineStr">
         <is>
-          <t>가족 반찬에 채소 하나</t>
+          <t>상 차릴 때 채소 하나 더</t>
         </is>
       </c>
       <c r="G178" s="15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>함께 먹는 반찬이 늘면 나도 늘어요.</t>
+          <t>상에 오르는 채소가 늘면 먹는 채소도 늘어요.</t>
         </is>
       </c>
       <c r="I178" s="1" t="inlineStr">
@@ -13930,7 +13954,11 @@
         </is>
       </c>
       <c r="M178" s="1" t="n"/>
-      <c r="N178" s="3" t="n"/>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O178" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0212</t>
@@ -13970,7 +13998,7 @@
       </c>
       <c r="F179" s="1" t="inlineStr">
         <is>
-          <t>국은 각자 그릇에 덜기</t>
+          <t>국은 그릇에 덜어 먹기</t>
         </is>
       </c>
       <c r="G179" s="1" t="n">
@@ -14002,7 +14030,11 @@
         </is>
       </c>
       <c r="M179" s="1" t="n"/>
-      <c r="N179" s="3" t="n"/>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
+          <t>10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
+        </is>
+      </c>
       <c r="O179" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0213</t>
@@ -14114,11 +14146,11 @@
       </c>
       <c r="F181" s="1" t="inlineStr">
         <is>
-          <t>면 국물은 반만</t>
+          <t>국물 음식은 절반만</t>
         </is>
       </c>
       <c r="G181" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
@@ -14148,7 +14180,7 @@
       <c r="M181" s="1" t="n"/>
       <c r="N181" s="3" t="inlineStr">
         <is>
-          <t>10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="O181" s="6" t="inlineStr">
@@ -21680,7 +21712,7 @@
       </c>
       <c r="F280" s="18" t="inlineStr">
         <is>
-          <t>함께 먹는 끼니 정하기</t>
+          <t>하루 한 끼는 여유 있게</t>
         </is>
       </c>
       <c r="G280" s="18">
@@ -21689,7 +21721,7 @@
       </c>
       <c r="H280" s="17" t="inlineStr">
         <is>
-          <t>함께 먹으면 천천히, 즐겁게 먹게 돼요.</t>
+          <t>끼니 하나를 정해 두면 천천히 즐겁게 먹게 돼요.</t>
         </is>
       </c>
       <c r="I280" s="18" t="inlineStr">
@@ -21715,7 +21747,7 @@
       <c r="M280" s="18" t="n"/>
       <c r="N280" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 55번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인</t>
+          <t>2026-10-13 추가(검수표 55번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="O280" s="18" t="inlineStr">
@@ -22912,7 +22944,7 @@
       </c>
       <c r="F296" s="18" t="inlineStr">
         <is>
-          <t>면 요리에 채소 넣기</t>
+          <t>끓일 때 채소 한 줌 넣기</t>
         </is>
       </c>
       <c r="G296" s="18">
@@ -22947,7 +22979,7 @@
       <c r="M296" s="18" t="n"/>
       <c r="N296" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 71번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 71번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="O296" s="18" t="inlineStr">
@@ -25546,7 +25578,7 @@
       </c>
       <c r="F330" s="18" t="inlineStr">
         <is>
-          <t>도시락에 단백질 담기</t>
+          <t>내일 단백질 반찬 담기</t>
         </is>
       </c>
       <c r="G330" s="18">
@@ -25555,7 +25587,7 @@
       </c>
       <c r="H330" s="17" t="inlineStr">
         <is>
-          <t>도시락에 담으면 밖에서도 단백질을 챙겨요.</t>
+          <t>미리 담아 두면 밖에서도 단백질을 챙겨요.</t>
         </is>
       </c>
       <c r="I330" s="18" t="inlineStr">
@@ -25581,7 +25613,7 @@
       <c r="M330" s="18" t="n"/>
       <c r="N330" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 105번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인</t>
+          <t>2026-10-13 추가(검수표 105번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="O330" s="18" t="inlineStr">
@@ -26778,7 +26810,7 @@
       </c>
       <c r="F346" s="18" t="inlineStr">
         <is>
-          <t>면 요리에 콩나물 한 줌</t>
+          <t>끓일 때 콩나물 한 줌</t>
         </is>
       </c>
       <c r="G346" s="18">
@@ -26787,7 +26819,7 @@
       </c>
       <c r="H346" s="17" t="inlineStr">
         <is>
-          <t>콩나물을 넣으면 면 요리에도 채소가 더해져요.</t>
+          <t>콩나물을 넣으면 한 그릇에 채소가 더해져요.</t>
         </is>
       </c>
       <c r="I346" s="18" t="inlineStr">
@@ -26813,7 +26845,7 @@
       <c r="M346" s="18" t="n"/>
       <c r="N346" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 121번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 121번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="O346" s="18" t="inlineStr">
@@ -27009,7 +27041,7 @@
       </c>
       <c r="F349" s="18" t="inlineStr">
         <is>
-          <t>면 요리에 달걀 하나</t>
+          <t>끓일 때 달걀 하나 넣기</t>
         </is>
       </c>
       <c r="G349" s="18">
@@ -27018,7 +27050,7 @@
       </c>
       <c r="H349" s="17" t="inlineStr">
         <is>
-          <t>달걀을 넣으면 면 요리에도 단백질이 더해져요.</t>
+          <t>달걀을 넣으면 한 그릇에 단백질이 더해져요.</t>
         </is>
       </c>
       <c r="I349" s="18" t="inlineStr">
@@ -27044,7 +27076,7 @@
       <c r="M349" s="18" t="n"/>
       <c r="N349" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 124번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 124번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="O349" s="18" t="inlineStr">
@@ -27475,7 +27507,7 @@
       </c>
       <c r="F355" s="18" t="inlineStr">
         <is>
-          <t>분말 스프는 반만</t>
+          <t>양념은 절반만 넣기</t>
         </is>
       </c>
       <c r="G355" s="18">
@@ -27484,7 +27516,7 @@
       </c>
       <c r="H355" s="17" t="inlineStr">
         <is>
-          <t>스프를 반만 넣으면 나트륨이 크게 줄어요.</t>
+          <t>양념을 반만 넣으면 나트륨이 크게 줄어요.</t>
         </is>
       </c>
       <c r="I355" s="18" t="inlineStr">
@@ -27510,7 +27542,7 @@
       <c r="M355" s="18" t="n"/>
       <c r="N355" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 130번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 130번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="O355" s="18" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -15118,15 +15118,15 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>마가린·쇼트닝 빼기</t>
+          <t>트랜스지방 없는 하루</t>
         </is>
       </c>
       <c r="G194" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>트랜스지방이 많은 기름을 빼는 행동이에요.</t>
+          <t>트랜스지방이 든 기름을 하루 쓰지 않는 행동이에요.</t>
         </is>
       </c>
       <c r="I194" s="6" t="inlineStr">
@@ -15152,7 +15152,7 @@
       <c r="M194" s="6" t="n"/>
       <c r="N194" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0241</t>
+          <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0241 · 10-19 「없는 하루」 꼴로</t>
         </is>
       </c>
       <c r="O194" s="6" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -1382,7 +1382,11 @@
         </is>
       </c>
       <c r="M6" s="1" t="n"/>
-      <c r="N6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>10-19 「A 대신 B」꼴은 기본 단계로</t>
+        </is>
+      </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0044</t>
@@ -1772,7 +1776,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -1814,7 +1818,11 @@
         </is>
       </c>
       <c r="M12" s="1" t="n"/>
-      <c r="N12" s="3" t="n"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>10-19 「A 대신 B」꼴은 기본 단계로</t>
+        </is>
+      </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0050</t>
@@ -3680,7 +3688,7 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
@@ -3722,7 +3730,11 @@
         </is>
       </c>
       <c r="M38" s="1" t="n"/>
-      <c r="N38" s="3" t="n"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>10-19 「A 대신 B」꼴은 기본 단계로</t>
+        </is>
+      </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0075</t>
@@ -7404,7 +7416,7 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -7446,7 +7458,11 @@
         </is>
       </c>
       <c r="M89" s="1" t="n"/>
-      <c r="N89" s="3" t="n"/>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
+          <t>10-19 「A 대신 B」꼴은 기본 단계로</t>
+        </is>
+      </c>
       <c r="O89" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0126</t>
@@ -16552,7 +16568,7 @@
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
@@ -16596,7 +16612,7 @@
       <c r="M213" s="6" t="n"/>
       <c r="N213" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0260</t>
+          <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0260 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O213" s="6" t="inlineStr">
@@ -18772,7 +18788,7 @@
       </c>
       <c r="D242" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E242" s="18" t="inlineStr">
@@ -18817,7 +18833,7 @@
       <c r="M242" s="18" t="n"/>
       <c r="N242" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 17번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인</t>
+          <t>2026-10-13 추가(검수표 17번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O242" s="18" t="inlineStr">
@@ -19388,7 +19404,7 @@
       </c>
       <c r="D250" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E250" s="18" t="inlineStr">
@@ -19437,7 +19453,7 @@
       </c>
       <c r="N250" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 25번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인</t>
+          <t>2026-10-13 추가(검수표 25번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O250" s="18" t="inlineStr">
@@ -19469,7 +19485,7 @@
       </c>
       <c r="D251" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E251" s="18" t="inlineStr">
@@ -19514,7 +19530,7 @@
       <c r="M251" s="18" t="n"/>
       <c r="N251" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 26번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인</t>
+          <t>2026-10-13 추가(검수표 26번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O251" s="18" t="inlineStr">
@@ -21481,7 +21497,7 @@
       </c>
       <c r="F277" s="18" t="inlineStr">
         <is>
-          <t>저녁은 매일 7시쯤</t>
+          <t>저녁은 매일 같은 시간에</t>
         </is>
       </c>
       <c r="G277" s="18">
@@ -21516,7 +21532,7 @@
       <c r="M277" s="18" t="n"/>
       <c r="N277" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 52번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인</t>
+          <t>2026-10-13 추가(검수표 52번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 시각 전제 없이</t>
         </is>
       </c>
       <c r="O277" s="18" t="inlineStr">
@@ -25645,7 +25661,7 @@
       </c>
       <c r="D331" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E331" s="18" t="inlineStr">
@@ -25690,7 +25706,7 @@
       <c r="M331" s="18" t="n"/>
       <c r="N331" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 106번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 106번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O331" s="18" t="inlineStr">
@@ -25722,7 +25738,7 @@
       </c>
       <c r="D332" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E332" s="18" t="inlineStr">
@@ -25767,7 +25783,7 @@
       <c r="M332" s="18" t="n"/>
       <c r="N332" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 107번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 107번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O332" s="18" t="inlineStr">
@@ -26030,7 +26046,7 @@
       </c>
       <c r="D336" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E336" s="18" t="inlineStr">
@@ -26075,7 +26091,7 @@
       <c r="M336" s="18" t="n"/>
       <c r="N336" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 111번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 111번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O336" s="18" t="inlineStr">
@@ -26107,7 +26123,7 @@
       </c>
       <c r="D337" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E337" s="18" t="inlineStr">
@@ -26152,7 +26168,7 @@
       <c r="M337" s="18" t="n"/>
       <c r="N337" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 112번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 112번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O337" s="18" t="inlineStr">
@@ -26184,7 +26200,7 @@
       </c>
       <c r="D338" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E338" s="18" t="inlineStr">
@@ -26229,7 +26245,7 @@
       <c r="M338" s="18" t="n"/>
       <c r="N338" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 113번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 113번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O338" s="18" t="inlineStr">
@@ -26261,7 +26277,7 @@
       </c>
       <c r="D339" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E339" s="18" t="inlineStr">
@@ -26306,7 +26322,7 @@
       <c r="M339" s="18" t="n"/>
       <c r="N339" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 114번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 114번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O339" s="18" t="inlineStr">
@@ -26338,7 +26354,7 @@
       </c>
       <c r="D340" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E340" s="18" t="inlineStr">
@@ -26383,7 +26399,7 @@
       <c r="M340" s="18" t="n"/>
       <c r="N340" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 115번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 115번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O340" s="18" t="inlineStr">
@@ -26415,7 +26431,7 @@
       </c>
       <c r="D341" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E341" s="18" t="inlineStr">
@@ -26460,7 +26476,7 @@
       <c r="M341" s="18" t="n"/>
       <c r="N341" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 116번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 116번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O341" s="18" t="inlineStr">
@@ -26492,7 +26508,7 @@
       </c>
       <c r="D342" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E342" s="18" t="inlineStr">
@@ -26537,7 +26553,7 @@
       <c r="M342" s="18" t="n"/>
       <c r="N342" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 117번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 117번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O342" s="18" t="inlineStr">
@@ -27262,7 +27278,7 @@
       </c>
       <c r="D352" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E352" s="18" t="inlineStr">
@@ -27311,7 +27327,7 @@
       </c>
       <c r="N352" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 127번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 127번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O352" s="18" t="inlineStr">
@@ -27651,7 +27667,7 @@
       </c>
       <c r="D357" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E357" s="18" t="inlineStr">
@@ -27696,7 +27712,7 @@
       <c r="M357" s="18" t="n"/>
       <c r="N357" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 132번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 132번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O357" s="18" t="inlineStr">
@@ -27728,7 +27744,7 @@
       </c>
       <c r="D358" s="18" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E358" s="18" t="inlineStr">
@@ -27773,7 +27789,7 @@
       <c r="M358" s="18" t="n"/>
       <c r="N358" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 133번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>2026-10-13 추가(검수표 133번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="O358" s="18" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -1498,11 +1498,11 @@
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>외식에도 채소 하나 더</t>
+          <t>외식 메뉴는 채소 위주로</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1530,7 +1530,11 @@
         </is>
       </c>
       <c r="M8" s="1" t="n"/>
-      <c r="N8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>10-19 외식 메뉴 고르기로</t>
+        </is>
+      </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
           <t>DIET-P-0046</t>

--- a/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -1498,11 +1498,11 @@
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>외식 메뉴는 채소 위주로</t>
+          <t>외식 메뉴, 채소 곁들이기</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       <c r="M8" s="1" t="n"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>10-19 외식 메뉴 고르기로</t>
+          <t>10-19 외식 메뉴 고르기로 · 10-19 외식 메뉴에 채소 곁들이기로</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -18956,7 +18956,7 @@
       </c>
       <c r="F244" s="18" t="inlineStr">
         <is>
-          <t>먹기 편한 시간 적기</t>
+          <t>먹기 편한 시간 적어보기</t>
         </is>
       </c>
       <c r="G244" s="18">
@@ -18991,7 +18991,7 @@
       <c r="M244" s="18" t="n"/>
       <c r="N244" s="17" t="inlineStr">
         <is>
-          <t>2026-10-13 추가(검수표 19번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인</t>
+          <t>2026-10-13 추가(검수표 19번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인 · 10-19 「적어보기」로</t>
         </is>
       </c>
       <c r="O244" s="18" t="inlineStr">
